--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/1500000/Output_0_9.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/1500000/Output_0_9.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>320071.425633411</v>
+        <v>320074.8015362157</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2995127.424547405</v>
+        <v>2995243.613506389</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20355556.36745723</v>
+        <v>20355670.24425593</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4812396.678818937</v>
+        <v>4812058.02286789</v>
       </c>
     </row>
     <row r="11">
@@ -1123,13 +1123,13 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>10.95151064538747</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="D8" t="n">
-        <v>26</v>
+        <v>12.57565326968602</v>
       </c>
       <c r="E8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1141,10 +1141,10 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J8" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1165,10 +1165,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1189,7 +1189,7 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
     </row>
     <row r="9">
@@ -1211,16 +1211,16 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>22.15420867374215</v>
+        <v>21.81976115797297</v>
       </c>
       <c r="G9" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="H9" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="I9" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J9" t="n">
         <v>0.7465913262578567</v>
@@ -1293,16 +1293,16 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>22.54368386855027</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1320,19 +1320,19 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>19.84491174912431</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1405,16 +1405,16 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>22.90079999999999</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="S11" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T11" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="U11" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1448,16 +1448,16 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1484,16 +1484,16 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>22.90079999999999</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1533,16 +1533,16 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>23.5527513075609</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1560,16 +1560,16 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>19.84491174912431</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1642,16 +1642,16 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>22.90079999999999</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="S14" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T14" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="U14" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1697,7 +1697,7 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1721,16 +1721,16 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S15" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T15" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="U15" t="n">
-        <v>22.15420867374214</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1767,19 +1767,19 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.27419204266741</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1797,16 +1797,16 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -1879,16 +1879,16 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="S17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="T17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="U17" t="n">
-        <v>14.67170078545518</v>
+        <v>14.31059503474164</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1919,19 +1919,19 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1958,10 +1958,10 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>24.66239999999999</v>
+        <v>24.30129424928645</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
@@ -1989,7 +1989,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22.02246762618611</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -2007,7 +2007,7 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>22.44875936050941</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -2049,16 +2049,16 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="W19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
     </row>
     <row r="20">
@@ -2074,25 +2074,25 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>200.3360962888297</v>
       </c>
       <c r="E20" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2119,10 +2119,10 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>19.70106086546267</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -2137,7 +2137,7 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2147,13 +2147,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C21" t="n">
-        <v>56.87573693824336</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -2165,13 +2165,13 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>35.33690566337831</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2195,28 +2195,28 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U21" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2289,10 +2289,10 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="X22" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
@@ -2314,22 +2314,22 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>200.3235106453875</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2350,22 +2350,22 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>102.3382270926889</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
@@ -2374,7 +2374,7 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2387,16 +2387,16 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C24" t="n">
-        <v>172.7084989883157</v>
+        <v>121.9333552767668</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -2405,10 +2405,10 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>20.72922793029332</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2432,13 +2432,13 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2447,13 +2447,13 @@
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="25">
@@ -2511,7 +2511,7 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -2554,19 +2554,19 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>50.45439270423778</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -2590,7 +2590,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -2602,16 +2602,16 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>212.285385643442</v>
       </c>
       <c r="W26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="27">
@@ -2627,25 +2627,25 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>157.6450804554009</v>
+        <v>101.4502042303408</v>
       </c>
       <c r="F27" t="n">
         <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H27" t="n">
-        <v>80.62968333331338</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -2672,7 +2672,7 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
         <v>0</v>
@@ -2690,7 +2690,7 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="28">
@@ -2721,7 +2721,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2763,7 +2763,7 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -2779,19 +2779,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>212.285385643442</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E29" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F29" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -2833,7 +2833,7 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>230.1769504358685</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2858,28 +2858,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F30" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I30" t="n">
-        <v>4.279209191128717</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>58.46192485583209</v>
       </c>
       <c r="T30" t="n">
         <v>0</v>
@@ -2918,16 +2918,16 @@
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W30" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2955,58 +2955,58 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -3031,13 +3031,13 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="H32" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>29.51218284430544</v>
+        <v>196.0929612559941</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3061,19 +3061,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="U32" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>142.9833274914823</v>
       </c>
       <c r="G33" t="n">
-        <v>99.62076558201635</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -3143,28 +3143,28 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T33" t="n">
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="V33" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="34">
@@ -3216,13 +3216,13 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>44.30348359856706</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
         <v>0</v>
@@ -3256,16 +3256,16 @@
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>35.4921132580601</v>
+        <v>179.7283339446665</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -3301,10 +3301,10 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R35" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
@@ -3322,7 +3322,7 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
     </row>
     <row r="36">
@@ -3332,25 +3332,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>6.815205755865338</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -3389,16 +3389,16 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>89.21416584735675</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
         <v>0</v>
@@ -3456,10 +3456,10 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>47.02492433367367</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
         <v>0</v>
@@ -3490,25 +3490,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3541,7 +3541,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>189.372</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -3553,13 +3553,13 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>189.7190331592112</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
     </row>
     <row r="39">
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -3584,16 +3584,16 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>105.6174592896822</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -3620,25 +3620,25 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>61.34578705948491</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U39" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -3669,34 +3669,34 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -3739,10 +3739,10 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>184.1237416288039</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="G41" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -3772,13 +3772,13 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
@@ -3796,7 +3796,7 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>190.9324654410926</v>
       </c>
     </row>
     <row r="42">
@@ -3815,22 +3815,22 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>157.6450804554009</v>
+        <v>50.56615741463719</v>
       </c>
       <c r="F42" t="n">
         <v>145.0692123933839</v>
       </c>
       <c r="G42" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>13.95809886308724</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -3857,22 +3857,22 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y42" t="n">
         <v>0</v>
@@ -3885,7 +3885,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -3936,7 +3936,7 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -4763,76 +4763,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>77.73737373737373</v>
+        <v>66.51046739551762</v>
       </c>
       <c r="C8" t="n">
-        <v>66.67524177233588</v>
+        <v>40.631385380739</v>
       </c>
       <c r="D8" t="n">
-        <v>40.41261550970962</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="E8" t="n">
-        <v>14.14998924708335</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="F8" t="n">
-        <v>14.14998924708335</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="G8" t="n">
-        <v>14.14998924708335</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="H8" t="n">
-        <v>14.14998924708335</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="I8" t="n">
-        <v>14.14998924708335</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J8" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K8" t="n">
-        <v>27.82</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="L8" t="n">
-        <v>27.82</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="M8" t="n">
-        <v>53.56</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="N8" t="n">
-        <v>78.26000000000001</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="O8" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P8" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q8" t="n">
-        <v>104</v>
+        <v>92.38954941029624</v>
       </c>
       <c r="R8" t="n">
-        <v>77.73737373737373</v>
+        <v>92.38954941029624</v>
       </c>
       <c r="S8" t="n">
-        <v>77.73737373737373</v>
+        <v>92.38954941029624</v>
       </c>
       <c r="T8" t="n">
-        <v>77.73737373737373</v>
+        <v>92.38954941029624</v>
       </c>
       <c r="U8" t="n">
-        <v>77.73737373737373</v>
+        <v>92.38954941029624</v>
       </c>
       <c r="V8" t="n">
-        <v>77.73737373737373</v>
+        <v>92.38954941029624</v>
       </c>
       <c r="W8" t="n">
-        <v>77.73737373737373</v>
+        <v>92.38954941029624</v>
       </c>
       <c r="X8" t="n">
-        <v>77.73737373737373</v>
+        <v>92.38954941029624</v>
       </c>
       <c r="Y8" t="n">
-        <v>77.73737373737373</v>
+        <v>66.51046739551762</v>
       </c>
     </row>
     <row r="9">
@@ -4842,76 +4842,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="C9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="D9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="E9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="F9" t="n">
-        <v>81.62201144066449</v>
+        <v>80.44100199269204</v>
       </c>
       <c r="G9" t="n">
-        <v>55.35938517803824</v>
+        <v>54.56191997791342</v>
       </c>
       <c r="H9" t="n">
-        <v>29.09675891541198</v>
+        <v>28.6828379631348</v>
       </c>
       <c r="I9" t="n">
-        <v>2.834132652785714</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="J9" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K9" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L9" t="n">
-        <v>27.82</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="M9" t="n">
-        <v>53.56</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="N9" t="n">
-        <v>78.26000000000001</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="O9" t="n">
-        <v>78.26000000000001</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="P9" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="Q9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
     </row>
     <row r="10">
@@ -4921,76 +4921,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C10" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D10" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E10" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F10" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G10" t="n">
-        <v>81.22860215297952</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H10" t="n">
-        <v>54.96597589035326</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I10" t="n">
-        <v>28.70334962772699</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J10" t="n">
-        <v>2.44072336510073</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K10" t="n">
-        <v>2.44072336510073</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L10" t="n">
-        <v>28.18072336510073</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M10" t="n">
-        <v>53.92072336510073</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N10" t="n">
-        <v>79.66072336510072</v>
+        <v>78.14188814362404</v>
       </c>
       <c r="O10" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P10" t="n">
-        <v>104</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="Q10" t="n">
-        <v>104</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="R10" t="n">
-        <v>104</v>
+        <v>47.97407071350496</v>
       </c>
       <c r="S10" t="n">
-        <v>104</v>
+        <v>22.09498869872634</v>
       </c>
       <c r="T10" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="U10" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="V10" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="W10" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="X10" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y10" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="11">
@@ -5000,76 +5000,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L11" t="n">
-        <v>26.78000000000001</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M11" t="n">
-        <v>26.78000000000001</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="N11" t="n">
-        <v>52.52000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="O11" t="n">
-        <v>78.26000000000001</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R11" t="n">
-        <v>80.86787878787879</v>
+        <v>79.68686933990632</v>
       </c>
       <c r="S11" t="n">
-        <v>54.60525252525252</v>
+        <v>53.80778732512771</v>
       </c>
       <c r="T11" t="n">
-        <v>28.34262626262626</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="U11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="V11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="W11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="X11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="12">
@@ -5079,76 +5079,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.08</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="C12" t="n">
-        <v>2.08</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="D12" t="n">
-        <v>2.08</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="E12" t="n">
-        <v>2.08</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="F12" t="n">
-        <v>2.08</v>
+        <v>79.68686933990632</v>
       </c>
       <c r="G12" t="n">
-        <v>2.08</v>
+        <v>53.80778732512771</v>
       </c>
       <c r="H12" t="n">
-        <v>2.08</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="I12" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J12" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K12" t="n">
-        <v>27.82</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L12" t="n">
-        <v>53.56</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M12" t="n">
-        <v>79.3</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N12" t="n">
-        <v>104</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="O12" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P12" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q12" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R12" t="n">
-        <v>77.73737373737373</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S12" t="n">
-        <v>51.47474747474747</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T12" t="n">
-        <v>25.2121212121212</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U12" t="n">
-        <v>2.08</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V12" t="n">
-        <v>2.08</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W12" t="n">
-        <v>2.08</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X12" t="n">
-        <v>2.08</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.08</v>
+        <v>102.4811647785233</v>
       </c>
     </row>
     <row r="13">
@@ -5158,76 +5158,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>100.8903465994381</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C13" t="n">
-        <v>100.8903465994381</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D13" t="n">
-        <v>100.8903465994381</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E13" t="n">
-        <v>100.8903465994381</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F13" t="n">
-        <v>100.8903465994381</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G13" t="n">
-        <v>100.8903465994381</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H13" t="n">
-        <v>77.09968871301299</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I13" t="n">
-        <v>50.83706245038672</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J13" t="n">
-        <v>24.57443618776046</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K13" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L13" t="n">
-        <v>27.82</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M13" t="n">
-        <v>53.56</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N13" t="n">
-        <v>79.3</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="O13" t="n">
-        <v>103.6392766348993</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P13" t="n">
-        <v>100.8903465994381</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="Q13" t="n">
-        <v>100.8903465994381</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="R13" t="n">
-        <v>100.8903465994381</v>
+        <v>47.97407071350496</v>
       </c>
       <c r="S13" t="n">
-        <v>100.8903465994381</v>
+        <v>22.09498869872634</v>
       </c>
       <c r="T13" t="n">
-        <v>100.8903465994381</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="U13" t="n">
-        <v>100.8903465994381</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="V13" t="n">
-        <v>100.8903465994381</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="W13" t="n">
-        <v>100.8903465994381</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="X13" t="n">
-        <v>100.8903465994381</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y13" t="n">
-        <v>100.8903465994381</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="14">
@@ -5237,76 +5237,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K14" t="n">
-        <v>27.82</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L14" t="n">
-        <v>53.56</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M14" t="n">
-        <v>78.26000000000001</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N14" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="O14" t="n">
-        <v>78.26000000000001</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R14" t="n">
-        <v>80.86787878787879</v>
+        <v>79.68686933990632</v>
       </c>
       <c r="S14" t="n">
-        <v>54.60525252525252</v>
+        <v>53.80778732512771</v>
       </c>
       <c r="T14" t="n">
-        <v>28.34262626262626</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="U14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="V14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="W14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="X14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="15">
@@ -5316,76 +5316,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.834132652785714</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C15" t="n">
-        <v>2.834132652785714</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D15" t="n">
-        <v>2.834132652785714</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E15" t="n">
-        <v>2.834132652785714</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F15" t="n">
-        <v>2.834132652785714</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G15" t="n">
-        <v>2.834132652785714</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H15" t="n">
-        <v>2.834132652785714</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I15" t="n">
-        <v>2.834132652785714</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K15" t="n">
-        <v>2.08</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="L15" t="n">
-        <v>2.08</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="M15" t="n">
-        <v>27.82</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="N15" t="n">
-        <v>53.56</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="O15" t="n">
-        <v>78.26000000000001</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="P15" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="Q15" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R15" t="n">
-        <v>77.73737373737373</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="S15" t="n">
-        <v>51.47474747474747</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="T15" t="n">
-        <v>25.2121212121212</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="U15" t="n">
-        <v>2.834132652785714</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="V15" t="n">
-        <v>2.834132652785714</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="W15" t="n">
-        <v>2.834132652785714</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="X15" t="n">
-        <v>2.834132652785714</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.834132652785714</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="16">
@@ -5395,76 +5395,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>103.6392766348993</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C16" t="n">
-        <v>103.6392766348993</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D16" t="n">
-        <v>103.6392766348993</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E16" t="n">
-        <v>103.6392766348993</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F16" t="n">
-        <v>103.6392766348993</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G16" t="n">
-        <v>103.3623149756393</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H16" t="n">
-        <v>77.09968871301299</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I16" t="n">
-        <v>50.83706245038672</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J16" t="n">
-        <v>24.57443618776046</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K16" t="n">
-        <v>2.08</v>
+        <v>2.049623295570477</v>
       </c>
       <c r="L16" t="n">
-        <v>27.82</v>
+        <v>27.413711578255</v>
       </c>
       <c r="M16" t="n">
-        <v>53.56</v>
+        <v>52.77779986093952</v>
       </c>
       <c r="N16" t="n">
-        <v>79.3</v>
+        <v>78.14188814362404</v>
       </c>
       <c r="O16" t="n">
-        <v>103.6392766348993</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P16" t="n">
-        <v>103.6392766348993</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q16" t="n">
-        <v>103.6392766348993</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="R16" t="n">
-        <v>103.6392766348993</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="S16" t="n">
-        <v>103.6392766348993</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="T16" t="n">
-        <v>103.6392766348993</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="U16" t="n">
-        <v>103.6392766348993</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="V16" t="n">
-        <v>103.6392766348993</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="W16" t="n">
-        <v>103.6392766348993</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="X16" t="n">
-        <v>103.6392766348993</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y16" t="n">
-        <v>103.6392766348993</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="17">
@@ -5474,76 +5474,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="C17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="D17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="E17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="F17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="G17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K17" t="n">
-        <v>29.96</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L17" t="n">
-        <v>29.96</v>
+        <v>28.41772601812563</v>
       </c>
       <c r="M17" t="n">
-        <v>56.56</v>
+        <v>55.73185102583861</v>
       </c>
       <c r="N17" t="n">
-        <v>84.28</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="O17" t="n">
-        <v>84.28</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="P17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q17" t="n">
-        <v>101.9083846317729</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="R17" t="n">
-        <v>73.62555634894463</v>
+        <v>72.39977328887976</v>
       </c>
       <c r="S17" t="n">
-        <v>45.34272806611634</v>
+        <v>44.53106090472204</v>
       </c>
       <c r="T17" t="n">
-        <v>17.05989978328806</v>
+        <v>16.66234852056432</v>
       </c>
       <c r="U17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="V17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="W17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="X17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
     </row>
     <row r="18">
@@ -5553,76 +5553,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>58.80565656565657</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="C18" t="n">
-        <v>58.80565656565657</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="D18" t="n">
-        <v>58.80565656565657</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="E18" t="n">
-        <v>30.52282828282829</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="F18" t="n">
-        <v>2.24</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="G18" t="n">
-        <v>2.24</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="H18" t="n">
-        <v>2.24</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="I18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L18" t="n">
-        <v>2.24</v>
+        <v>28.41772601812563</v>
       </c>
       <c r="M18" t="n">
-        <v>28.84</v>
+        <v>55.73185102583861</v>
       </c>
       <c r="N18" t="n">
-        <v>56.56</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="O18" t="n">
-        <v>84.28</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="P18" t="n">
-        <v>84.28</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q18" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R18" t="n">
-        <v>83.71717171717171</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="S18" t="n">
-        <v>58.80565656565657</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="T18" t="n">
-        <v>58.80565656565657</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="U18" t="n">
-        <v>58.80565656565657</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="V18" t="n">
-        <v>58.80565656565657</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="W18" t="n">
-        <v>58.80565656565657</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="X18" t="n">
-        <v>58.80565656565657</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="Y18" t="n">
-        <v>58.80565656565657</v>
+        <v>85.81333917329844</v>
       </c>
     </row>
     <row r="19">
@@ -5632,76 +5632,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.24</v>
+        <v>24.88271652639035</v>
       </c>
       <c r="C19" t="n">
-        <v>2.24</v>
+        <v>24.88271652639035</v>
       </c>
       <c r="D19" t="n">
-        <v>2.24</v>
+        <v>24.88271652639035</v>
       </c>
       <c r="E19" t="n">
-        <v>2.24</v>
+        <v>24.88271652639035</v>
       </c>
       <c r="F19" t="n">
-        <v>2.24</v>
+        <v>24.88271652639035</v>
       </c>
       <c r="G19" t="n">
-        <v>2.24</v>
+        <v>24.88271652639035</v>
       </c>
       <c r="H19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L19" t="n">
-        <v>29.55412500771298</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M19" t="n">
-        <v>57.27412500771297</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="N19" t="n">
-        <v>84.99412500771297</v>
+        <v>84.14957704396423</v>
       </c>
       <c r="O19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="P19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="Q19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="R19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="S19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="T19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="U19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="V19" t="n">
-        <v>109.3334016426122</v>
+        <v>80.62014129470579</v>
       </c>
       <c r="W19" t="n">
-        <v>81.05057335978395</v>
+        <v>80.62014129470579</v>
       </c>
       <c r="X19" t="n">
-        <v>52.76774507695567</v>
+        <v>80.62014129470579</v>
       </c>
       <c r="Y19" t="n">
-        <v>24.48491679412739</v>
+        <v>52.75142891054807</v>
       </c>
     </row>
     <row r="20">
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>475.3162520913191</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C20" t="n">
-        <v>475.3162520913191</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="D20" t="n">
-        <v>475.3162520913191</v>
+        <v>761.6974622895962</v>
       </c>
       <c r="E20" t="n">
-        <v>231.8819086569757</v>
+        <v>518.2486856454962</v>
       </c>
       <c r="F20" t="n">
-        <v>231.8819086569757</v>
+        <v>274.7999090013961</v>
       </c>
       <c r="G20" t="n">
-        <v>231.8819086569757</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="H20" t="n">
-        <v>231.8819086569757</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="I20" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K20" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L20" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M20" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N20" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O20" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S20" t="n">
-        <v>944.0999385197347</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T20" t="n">
-        <v>718.7505955256626</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U20" t="n">
-        <v>718.7505955256626</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V20" t="n">
-        <v>718.7505955256626</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W20" t="n">
-        <v>718.7505955256626</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X20" t="n">
-        <v>718.7505955256626</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y20" t="n">
-        <v>475.3162520913191</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>76.73023933155895</v>
+        <v>492.48569440222</v>
       </c>
       <c r="C21" t="n">
-        <v>19.28</v>
+        <v>318.0326651210929</v>
       </c>
       <c r="D21" t="n">
-        <v>19.28</v>
+        <v>169.0982554598417</v>
       </c>
       <c r="E21" t="n">
-        <v>19.28</v>
+        <v>169.0982554598417</v>
       </c>
       <c r="F21" t="n">
-        <v>19.28</v>
+        <v>169.0982554598417</v>
       </c>
       <c r="G21" t="n">
-        <v>19.28</v>
+        <v>169.0982554598417</v>
       </c>
       <c r="H21" t="n">
-        <v>19.28</v>
+        <v>55.72911986742098</v>
       </c>
       <c r="I21" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K21" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L21" t="n">
-        <v>19.28</v>
+        <v>248.2447175439888</v>
       </c>
       <c r="M21" t="n">
-        <v>257.87</v>
+        <v>486.8488635328713</v>
       </c>
       <c r="N21" t="n">
-        <v>496.46</v>
+        <v>725.4530095217538</v>
       </c>
       <c r="O21" t="n">
-        <v>735.0500000000001</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P21" t="n">
-        <v>917.693477613351</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R21" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S21" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="T21" t="n">
-        <v>964</v>
+        <v>660.701031422288</v>
       </c>
       <c r="U21" t="n">
-        <v>735.7763817363891</v>
+        <v>660.701031422288</v>
       </c>
       <c r="V21" t="n">
-        <v>735.7763817363891</v>
+        <v>660.701031422288</v>
       </c>
       <c r="W21" t="n">
-        <v>492.3420383020457</v>
+        <v>660.701031422288</v>
       </c>
       <c r="X21" t="n">
-        <v>284.4905380965129</v>
+        <v>660.701031422288</v>
       </c>
       <c r="Y21" t="n">
-        <v>76.73023933155895</v>
+        <v>660.701031422288</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L22" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M22" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N22" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W22" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>720.5656565656566</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C23" t="n">
-        <v>720.5656565656566</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D23" t="n">
-        <v>720.5656565656566</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E23" t="n">
-        <v>477.1313131313132</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F23" t="n">
-        <v>233.6969696969697</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G23" t="n">
-        <v>233.6969696969697</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H23" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I23" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K23" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L23" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M23" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N23" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O23" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q23" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R23" t="n">
-        <v>964</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="S23" t="n">
-        <v>964</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="T23" t="n">
-        <v>964</v>
+        <v>366.1018663125844</v>
       </c>
       <c r="U23" t="n">
-        <v>964</v>
+        <v>122.6530896684844</v>
       </c>
       <c r="V23" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W23" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X23" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y23" t="n">
-        <v>720.5656565656566</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>521.1977889834866</v>
+        <v>142.4461484402802</v>
       </c>
       <c r="C24" t="n">
-        <v>346.7447597023596</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D24" t="n">
-        <v>346.7447597023596</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E24" t="n">
-        <v>187.5073046969041</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F24" t="n">
-        <v>40.97274672378907</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G24" t="n">
-        <v>40.97274672378907</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H24" t="n">
-        <v>40.97274672378907</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I24" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K24" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L24" t="n">
-        <v>19.28</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M24" t="n">
-        <v>257.87</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N24" t="n">
-        <v>496.46</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="O24" t="n">
-        <v>735.0500000000001</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P24" t="n">
-        <v>917.693477613351</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R24" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S24" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T24" t="n">
-        <v>689.4131260035546</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="U24" t="n">
-        <v>689.4131260035546</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="V24" t="n">
-        <v>689.4131260035546</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="W24" t="n">
-        <v>689.4131260035546</v>
+        <v>518.4217842253022</v>
       </c>
       <c r="X24" t="n">
-        <v>689.4131260035546</v>
+        <v>518.4217842253022</v>
       </c>
       <c r="Y24" t="n">
-        <v>689.4131260035546</v>
+        <v>310.6614854603483</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L25" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M25" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N25" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R25" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="S25" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T25" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U25" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>569.1827091503538</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="C26" t="n">
-        <v>569.1827091503538</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="D26" t="n">
-        <v>569.1827091503538</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="E26" t="n">
-        <v>569.1827091503538</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="F26" t="n">
-        <v>569.1827091503538</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G26" t="n">
-        <v>325.7483657160104</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H26" t="n">
-        <v>82.31402228166698</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I26" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K26" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L26" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M26" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N26" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O26" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R26" t="n">
-        <v>812.6170525846973</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S26" t="n">
-        <v>812.6170525846973</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T26" t="n">
-        <v>812.6170525846973</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U26" t="n">
-        <v>812.6170525846973</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V26" t="n">
-        <v>812.6170525846973</v>
+        <v>749.627473042513</v>
       </c>
       <c r="W26" t="n">
-        <v>569.1827091503538</v>
+        <v>749.627473042513</v>
       </c>
       <c r="X26" t="n">
-        <v>569.1827091503538</v>
+        <v>749.627473042513</v>
       </c>
       <c r="Y26" t="n">
-        <v>569.1827091503538</v>
+        <v>506.1786963984129</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>555.4305472189262</v>
+        <v>521.1447485139397</v>
       </c>
       <c r="C27" t="n">
-        <v>555.4305472189262</v>
+        <v>521.1447485139397</v>
       </c>
       <c r="D27" t="n">
-        <v>406.496137557675</v>
+        <v>521.1447485139397</v>
       </c>
       <c r="E27" t="n">
-        <v>247.2586825522195</v>
+        <v>418.6697947459187</v>
       </c>
       <c r="F27" t="n">
-        <v>100.7241245791044</v>
+        <v>272.1352367728036</v>
       </c>
       <c r="G27" t="n">
-        <v>100.7241245791044</v>
+        <v>133.4044113554191</v>
       </c>
       <c r="H27" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I27" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K27" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L27" t="n">
-        <v>144.6375600578374</v>
+        <v>178.8501590306595</v>
       </c>
       <c r="M27" t="n">
-        <v>383.2275600578374</v>
+        <v>417.4543050195419</v>
       </c>
       <c r="N27" t="n">
-        <v>621.8175600578375</v>
+        <v>656.0584510084244</v>
       </c>
       <c r="O27" t="n">
-        <v>860.4075600578375</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="P27" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S27" t="n">
-        <v>790.5826554506689</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T27" t="n">
-        <v>790.5826554506689</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U27" t="n">
-        <v>790.5826554506689</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V27" t="n">
-        <v>555.4305472189262</v>
+        <v>728.9050472788936</v>
       </c>
       <c r="W27" t="n">
-        <v>555.4305472189262</v>
+        <v>728.9050472788936</v>
       </c>
       <c r="X27" t="n">
-        <v>555.4305472189262</v>
+        <v>728.9050472788936</v>
       </c>
       <c r="Y27" t="n">
-        <v>555.4305472189262</v>
+        <v>521.1447485139397</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C28" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D28" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E28" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="F28" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="G28" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="H28" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="I28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L28" t="n">
-        <v>856.7818345174422</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M28" t="n">
-        <v>895.9698727096644</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N28" t="n">
-        <v>939.6607233651007</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W28" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X28" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y28" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>506.1486868686869</v>
+        <v>749.627473042513</v>
       </c>
       <c r="C29" t="n">
-        <v>506.1486868686869</v>
+        <v>749.627473042513</v>
       </c>
       <c r="D29" t="n">
-        <v>506.1486868686869</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="E29" t="n">
-        <v>262.7143434343434</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="F29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K29" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L29" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M29" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N29" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O29" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T29" t="n">
-        <v>738.6506570059279</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U29" t="n">
-        <v>738.6506570059279</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V29" t="n">
-        <v>738.6506570059279</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W29" t="n">
-        <v>738.6506570059279</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X29" t="n">
-        <v>738.6506570059279</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y29" t="n">
-        <v>506.1486868686869</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>344.5900207806347</v>
+        <v>669.8525979295682</v>
       </c>
       <c r="C30" t="n">
-        <v>170.1369914995077</v>
+        <v>669.8525979295682</v>
       </c>
       <c r="D30" t="n">
-        <v>170.1369914995077</v>
+        <v>520.918188268317</v>
       </c>
       <c r="E30" t="n">
-        <v>170.1369914995077</v>
+        <v>361.6807332628614</v>
       </c>
       <c r="F30" t="n">
-        <v>23.60243352639264</v>
+        <v>361.6807332628614</v>
       </c>
       <c r="G30" t="n">
-        <v>23.60243352639264</v>
+        <v>222.9499078454769</v>
       </c>
       <c r="H30" t="n">
-        <v>23.60243352639264</v>
+        <v>109.5807722530562</v>
       </c>
       <c r="I30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K30" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L30" t="n">
-        <v>144.6375600578374</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M30" t="n">
-        <v>234.7819638733197</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="N30" t="n">
-        <v>473.3719638733197</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="O30" t="n">
-        <v>711.9619638733197</v>
+        <v>851.8101010141643</v>
       </c>
       <c r="P30" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S30" t="n">
-        <v>964</v>
+        <v>905.0047061613109</v>
       </c>
       <c r="T30" t="n">
-        <v>964</v>
+        <v>905.0047061613109</v>
       </c>
       <c r="U30" t="n">
-        <v>964</v>
+        <v>905.0047061613109</v>
       </c>
       <c r="V30" t="n">
-        <v>964</v>
+        <v>669.8525979295682</v>
       </c>
       <c r="W30" t="n">
-        <v>720.5656565656566</v>
+        <v>669.8525979295682</v>
       </c>
       <c r="X30" t="n">
-        <v>720.5656565656566</v>
+        <v>669.8525979295682</v>
       </c>
       <c r="Y30" t="n">
-        <v>512.8053578007027</v>
+        <v>669.8525979295682</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C31" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D31" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E31" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F31" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G31" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L31" t="n">
-        <v>856.7818345174422</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M31" t="n">
-        <v>895.9698727096644</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N31" t="n">
-        <v>939.6607233651007</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y31" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>481.353720044753</v>
+        <v>432.8749126823416</v>
       </c>
       <c r="C32" t="n">
-        <v>481.353720044753</v>
+        <v>432.8749126823416</v>
       </c>
       <c r="D32" t="n">
-        <v>481.353720044753</v>
+        <v>432.8749126823416</v>
       </c>
       <c r="E32" t="n">
-        <v>481.353720044753</v>
+        <v>432.8749126823416</v>
       </c>
       <c r="F32" t="n">
-        <v>481.353720044753</v>
+        <v>432.8749126823416</v>
       </c>
       <c r="G32" t="n">
-        <v>264.1820028730358</v>
+        <v>215.3052180530201</v>
       </c>
       <c r="H32" t="n">
-        <v>47.01028570131862</v>
+        <v>215.3052180530201</v>
       </c>
       <c r="I32" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J32" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K32" t="n">
-        <v>22.36462077340309</v>
+        <v>23.55055379931807</v>
       </c>
       <c r="L32" t="n">
-        <v>202.4404723580617</v>
+        <v>203.6264053839766</v>
       </c>
       <c r="M32" t="n">
-        <v>415.2904723580617</v>
+        <v>416.8664630901746</v>
       </c>
       <c r="N32" t="n">
-        <v>621.144994565301</v>
+        <v>622.7209852974139</v>
       </c>
       <c r="O32" t="n">
-        <v>770.339944707949</v>
+        <v>771.915935440062</v>
       </c>
       <c r="P32" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q32" t="n">
-        <v>849.9083846317729</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R32" t="n">
-        <v>698.5254372164702</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S32" t="n">
-        <v>698.5254372164702</v>
+        <v>650.444607311663</v>
       </c>
       <c r="T32" t="n">
-        <v>698.5254372164702</v>
+        <v>432.8749126823416</v>
       </c>
       <c r="U32" t="n">
-        <v>481.353720044753</v>
+        <v>432.8749126823416</v>
       </c>
       <c r="V32" t="n">
-        <v>481.353720044753</v>
+        <v>432.8749126823416</v>
       </c>
       <c r="W32" t="n">
-        <v>481.353720044753</v>
+        <v>432.8749126823416</v>
       </c>
       <c r="X32" t="n">
-        <v>481.353720044753</v>
+        <v>432.8749126823416</v>
       </c>
       <c r="Y32" t="n">
-        <v>481.353720044753</v>
+        <v>432.8749126823416</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>266.7614456026819</v>
+        <v>161.6591233413921</v>
       </c>
       <c r="C33" t="n">
-        <v>266.7614456026819</v>
+        <v>161.6591233413921</v>
       </c>
       <c r="D33" t="n">
-        <v>117.8270359414307</v>
+        <v>161.6591233413921</v>
       </c>
       <c r="E33" t="n">
-        <v>117.8270359414307</v>
+        <v>161.6591233413921</v>
       </c>
       <c r="F33" t="n">
-        <v>117.8270359414307</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G33" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H33" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I33" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J33" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K33" t="n">
-        <v>17.2</v>
+        <v>142.5890798724797</v>
       </c>
       <c r="L33" t="n">
-        <v>17.2</v>
+        <v>355.8291375786776</v>
       </c>
       <c r="M33" t="n">
-        <v>230.05</v>
+        <v>569.0691952848756</v>
       </c>
       <c r="N33" t="n">
-        <v>442.9</v>
+        <v>569.0691952848756</v>
       </c>
       <c r="O33" t="n">
-        <v>655.75</v>
+        <v>782.3092529910735</v>
       </c>
       <c r="P33" t="n">
-        <v>838.3934776133508</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q33" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R33" t="n">
-        <v>860</v>
+        <v>760.4064612849986</v>
       </c>
       <c r="S33" t="n">
-        <v>860</v>
+        <v>586.9891167356675</v>
       </c>
       <c r="T33" t="n">
-        <v>860</v>
+        <v>586.9891167356675</v>
       </c>
       <c r="U33" t="n">
-        <v>860</v>
+        <v>369.419422106346</v>
       </c>
       <c r="V33" t="n">
-        <v>642.8282828282828</v>
+        <v>369.419422106346</v>
       </c>
       <c r="W33" t="n">
-        <v>642.8282828282828</v>
+        <v>369.419422106346</v>
       </c>
       <c r="X33" t="n">
-        <v>434.97678262275</v>
+        <v>369.419422106346</v>
       </c>
       <c r="Y33" t="n">
-        <v>434.97678262275</v>
+        <v>161.6591233413921</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>725.4677095097293</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="C34" t="n">
-        <v>725.4677095097293</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="D34" t="n">
-        <v>725.4677095097293</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="E34" t="n">
-        <v>725.4677095097293</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="F34" t="n">
-        <v>725.4677095097293</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="G34" t="n">
-        <v>725.4677095097293</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="H34" t="n">
-        <v>725.4677095097293</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="I34" t="n">
-        <v>725.4677095097293</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="J34" t="n">
-        <v>725.4677095097293</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="K34" t="n">
-        <v>725.4677095097293</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="L34" t="n">
-        <v>752.7818345174422</v>
+        <v>754.3578252495552</v>
       </c>
       <c r="M34" t="n">
-        <v>791.9698727096644</v>
+        <v>793.5458634417773</v>
       </c>
       <c r="N34" t="n">
-        <v>835.6607233651007</v>
+        <v>837.2367140972136</v>
       </c>
       <c r="O34" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="P34" t="n">
-        <v>860</v>
+        <v>858.8270606966518</v>
       </c>
       <c r="Q34" t="n">
-        <v>860</v>
+        <v>771.7946937757483</v>
       </c>
       <c r="R34" t="n">
-        <v>860</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="S34" t="n">
-        <v>860</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="T34" t="n">
-        <v>860</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="U34" t="n">
-        <v>860</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="V34" t="n">
-        <v>860</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="W34" t="n">
-        <v>860</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="X34" t="n">
-        <v>725.4677095097293</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="Y34" t="n">
-        <v>725.4677095097293</v>
+        <v>727.0437002418422</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>270.2223366243031</v>
+        <v>633.9146807345644</v>
       </c>
       <c r="C35" t="n">
-        <v>234.3717171717172</v>
+        <v>452.3709090732851</v>
       </c>
       <c r="D35" t="n">
-        <v>234.3717171717172</v>
+        <v>452.3709090732851</v>
       </c>
       <c r="E35" t="n">
-        <v>17.2</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="F35" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G35" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H35" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I35" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J35" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K35" t="n">
-        <v>120.2150059109224</v>
+        <v>23.55055379931807</v>
       </c>
       <c r="L35" t="n">
-        <v>202.4404723580617</v>
+        <v>203.6264053839766</v>
       </c>
       <c r="M35" t="n">
-        <v>415.2904723580617</v>
+        <v>416.8664630901746</v>
       </c>
       <c r="N35" t="n">
-        <v>621.144994565301</v>
+        <v>622.7209852974139</v>
       </c>
       <c r="O35" t="n">
-        <v>770.339944707949</v>
+        <v>771.915935440062</v>
       </c>
       <c r="P35" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q35" t="n">
-        <v>849.9083846317729</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="R35" t="n">
-        <v>698.5254372164702</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="S35" t="n">
-        <v>487.3940537960203</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="T35" t="n">
-        <v>487.3940537960203</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="U35" t="n">
-        <v>487.3940537960203</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="V35" t="n">
-        <v>487.3940537960203</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="W35" t="n">
-        <v>487.3940537960203</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="X35" t="n">
-        <v>487.3940537960203</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="Y35" t="n">
-        <v>270.2223366243031</v>
+        <v>633.9146807345644</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>17.2</v>
+        <v>592.1911242649305</v>
       </c>
       <c r="C36" t="n">
-        <v>17.2</v>
+        <v>585.3070780468847</v>
       </c>
       <c r="D36" t="n">
-        <v>17.2</v>
+        <v>436.3726683856335</v>
       </c>
       <c r="E36" t="n">
-        <v>17.2</v>
+        <v>277.135213380178</v>
       </c>
       <c r="F36" t="n">
-        <v>17.2</v>
+        <v>130.6006554070629</v>
       </c>
       <c r="G36" t="n">
-        <v>17.2</v>
+        <v>130.6006554070629</v>
       </c>
       <c r="H36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K36" t="n">
-        <v>142.5575600578374</v>
+        <v>142.5890798724797</v>
       </c>
       <c r="L36" t="n">
-        <v>355.4075600578374</v>
+        <v>355.8291375786776</v>
       </c>
       <c r="M36" t="n">
-        <v>568.2575600578374</v>
+        <v>569.0691952848756</v>
       </c>
       <c r="N36" t="n">
-        <v>677.3565223866492</v>
+        <v>678.932513118762</v>
       </c>
       <c r="O36" t="n">
-        <v>677.3565223866492</v>
+        <v>678.932513118762</v>
       </c>
       <c r="P36" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q36" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R36" t="n">
-        <v>758.8304705528857</v>
+        <v>760.4064612849986</v>
       </c>
       <c r="S36" t="n">
-        <v>758.8304705528857</v>
+        <v>760.4064612849986</v>
       </c>
       <c r="T36" t="n">
-        <v>758.8304705528857</v>
+        <v>760.4064612849986</v>
       </c>
       <c r="U36" t="n">
-        <v>541.6587533811685</v>
+        <v>760.4064612849986</v>
       </c>
       <c r="V36" t="n">
-        <v>324.4870362094513</v>
+        <v>760.4064612849986</v>
       </c>
       <c r="W36" t="n">
-        <v>107.3153190377341</v>
+        <v>760.4064612849986</v>
       </c>
       <c r="X36" t="n">
-        <v>17.2</v>
+        <v>760.4064612849986</v>
       </c>
       <c r="Y36" t="n">
-        <v>17.2</v>
+        <v>760.4064612849986</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="C37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="D37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="E37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="L37" t="n">
-        <v>44.51412500771298</v>
+        <v>44.54564482235524</v>
       </c>
       <c r="M37" t="n">
-        <v>83.70216319993516</v>
+        <v>83.73368301457742</v>
       </c>
       <c r="N37" t="n">
-        <v>127.3930138553715</v>
+        <v>127.4245336700137</v>
       </c>
       <c r="O37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="P37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="Q37" t="n">
-        <v>151.7322904902707</v>
+        <v>64.73144338400959</v>
       </c>
       <c r="R37" t="n">
-        <v>151.7322904902707</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="S37" t="n">
-        <v>151.7322904902707</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="T37" t="n">
-        <v>151.7322904902707</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="U37" t="n">
-        <v>151.7322904902707</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="V37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="W37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="X37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="Y37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>668.7151515151515</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="C38" t="n">
-        <v>668.7151515151515</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="D38" t="n">
-        <v>451.5434343434343</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="E38" t="n">
-        <v>234.3717171717172</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="F38" t="n">
-        <v>234.3717171717172</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="G38" t="n">
-        <v>17.2</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="H38" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I38" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J38" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K38" t="n">
-        <v>22.36462077340309</v>
+        <v>120.2465257255646</v>
       </c>
       <c r="L38" t="n">
-        <v>202.4404723580617</v>
+        <v>300.3223773102232</v>
       </c>
       <c r="M38" t="n">
-        <v>415.2904723580617</v>
+        <v>416.8664630901746</v>
       </c>
       <c r="N38" t="n">
-        <v>621.144994565301</v>
+        <v>622.7209852974139</v>
       </c>
       <c r="O38" t="n">
-        <v>770.339944707949</v>
+        <v>771.915935440062</v>
       </c>
       <c r="P38" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q38" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R38" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S38" t="n">
-        <v>668.7151515151515</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="T38" t="n">
-        <v>668.7151515151515</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="U38" t="n">
-        <v>668.7151515151515</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="V38" t="n">
-        <v>668.7151515151515</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="W38" t="n">
-        <v>668.7151515151515</v>
+        <v>669.9406037026066</v>
       </c>
       <c r="X38" t="n">
-        <v>668.7151515151515</v>
+        <v>669.9406037026066</v>
       </c>
       <c r="Y38" t="n">
-        <v>668.7151515151515</v>
+        <v>452.3709090732851</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>155.9308254173845</v>
+        <v>273.6043644414895</v>
       </c>
       <c r="C39" t="n">
-        <v>155.9308254173845</v>
+        <v>273.6043644414895</v>
       </c>
       <c r="D39" t="n">
-        <v>155.9308254173845</v>
+        <v>124.6699547802382</v>
       </c>
       <c r="E39" t="n">
-        <v>155.9308254173845</v>
+        <v>124.6699547802382</v>
       </c>
       <c r="F39" t="n">
-        <v>155.9308254173845</v>
+        <v>124.6699547802382</v>
       </c>
       <c r="G39" t="n">
-        <v>17.2</v>
+        <v>124.6699547802382</v>
       </c>
       <c r="H39" t="n">
-        <v>17.2</v>
+        <v>17.98565246742797</v>
       </c>
       <c r="I39" t="n">
-        <v>17.2</v>
+        <v>17.98565246742797</v>
       </c>
       <c r="J39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="L39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="M39" t="n">
-        <v>230.05</v>
+        <v>230.4715775208402</v>
       </c>
       <c r="N39" t="n">
-        <v>442.9</v>
+        <v>443.7116352270382</v>
       </c>
       <c r="O39" t="n">
-        <v>655.75</v>
+        <v>609.5379546054328</v>
       </c>
       <c r="P39" t="n">
-        <v>790.6054414866707</v>
+        <v>792.1814322187836</v>
       </c>
       <c r="Q39" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R39" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S39" t="n">
-        <v>798.0345585257728</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="T39" t="n">
-        <v>798.0345585257728</v>
+        <v>659.389396090879</v>
       </c>
       <c r="U39" t="n">
-        <v>580.8628413540556</v>
+        <v>659.389396090879</v>
       </c>
       <c r="V39" t="n">
-        <v>580.8628413540556</v>
+        <v>659.389396090879</v>
       </c>
       <c r="W39" t="n">
-        <v>363.6911241823384</v>
+        <v>441.8197014615575</v>
       </c>
       <c r="X39" t="n">
-        <v>363.6911241823384</v>
+        <v>441.8197014615575</v>
       </c>
       <c r="Y39" t="n">
-        <v>155.9308254173845</v>
+        <v>441.8197014615575</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>151.7322904902707</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="C40" t="n">
-        <v>151.7322904902707</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="D40" t="n">
-        <v>151.7322904902707</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="E40" t="n">
-        <v>151.7322904902707</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F40" t="n">
-        <v>151.7322904902707</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G40" t="n">
-        <v>151.7322904902707</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H40" t="n">
-        <v>151.7322904902707</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I40" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J40" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K40" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="L40" t="n">
-        <v>44.51412500771298</v>
+        <v>44.54564482235524</v>
       </c>
       <c r="M40" t="n">
-        <v>83.70216319993516</v>
+        <v>83.73368301457742</v>
       </c>
       <c r="N40" t="n">
-        <v>127.3930138553715</v>
+        <v>127.4245336700137</v>
       </c>
       <c r="O40" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="P40" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="Q40" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="R40" t="n">
-        <v>151.7322904902707</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="S40" t="n">
-        <v>151.7322904902707</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="T40" t="n">
-        <v>151.7322904902707</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="U40" t="n">
-        <v>151.7322904902707</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="V40" t="n">
-        <v>151.7322904902707</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="W40" t="n">
-        <v>151.7322904902707</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="X40" t="n">
-        <v>151.7322904902707</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="Y40" t="n">
-        <v>151.7322904902707</v>
+        <v>17.23151981464226</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>630.7770012113231</v>
+        <v>660.8359782662478</v>
       </c>
       <c r="C41" t="n">
-        <v>630.7770012113231</v>
+        <v>660.8359782662478</v>
       </c>
       <c r="D41" t="n">
-        <v>630.7770012113231</v>
+        <v>660.8359782662478</v>
       </c>
       <c r="E41" t="n">
-        <v>630.7770012113231</v>
+        <v>660.8359782662478</v>
       </c>
       <c r="F41" t="n">
-        <v>444.7934238084908</v>
+        <v>445.2559140063055</v>
       </c>
       <c r="G41" t="n">
-        <v>229.6419086569757</v>
+        <v>229.6758497463631</v>
       </c>
       <c r="H41" t="n">
-        <v>229.6419086569757</v>
+        <v>229.6758497463631</v>
       </c>
       <c r="I41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K41" t="n">
-        <v>120.0550059109223</v>
+        <v>17.62165426160527</v>
       </c>
       <c r="L41" t="n">
-        <v>196.4204723580617</v>
+        <v>197.6975058462639</v>
       </c>
       <c r="M41" t="n">
-        <v>407.2904723580617</v>
+        <v>408.9875268274333</v>
       </c>
       <c r="N41" t="n">
-        <v>613.144994565301</v>
+        <v>614.8420490346726</v>
       </c>
       <c r="O41" t="n">
-        <v>762.339944707949</v>
+        <v>764.0369991773207</v>
       </c>
       <c r="P41" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="Q41" t="n">
-        <v>841.9083846317729</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="R41" t="n">
-        <v>841.9083846317729</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="S41" t="n">
-        <v>630.7770012113231</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="T41" t="n">
-        <v>630.7770012113231</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="U41" t="n">
-        <v>630.7770012113231</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="V41" t="n">
-        <v>630.7770012113231</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="W41" t="n">
-        <v>630.7770012113231</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="X41" t="n">
-        <v>630.7770012113231</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="Y41" t="n">
-        <v>630.7770012113231</v>
+        <v>660.8359782662478</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>476.3960608094349</v>
+        <v>214.6854257439542</v>
       </c>
       <c r="C42" t="n">
-        <v>476.3960608094349</v>
+        <v>214.6854257439542</v>
       </c>
       <c r="D42" t="n">
-        <v>476.3960608094349</v>
+        <v>214.6854257439542</v>
       </c>
       <c r="E42" t="n">
-        <v>317.1586058039794</v>
+        <v>163.6084990625025</v>
       </c>
       <c r="F42" t="n">
-        <v>170.6240478308644</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="G42" t="n">
-        <v>31.89322241347989</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="H42" t="n">
-        <v>31.89322241347989</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="I42" t="n">
-        <v>17.79413265278571</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K42" t="n">
-        <v>17.04</v>
+        <v>142.4315011472248</v>
       </c>
       <c r="L42" t="n">
-        <v>227.91</v>
+        <v>248.4735348936818</v>
       </c>
       <c r="M42" t="n">
-        <v>227.91</v>
+        <v>248.4735348936818</v>
       </c>
       <c r="N42" t="n">
-        <v>389.0919638733197</v>
+        <v>459.7635558748512</v>
       </c>
       <c r="O42" t="n">
-        <v>599.9619638733197</v>
+        <v>671.0535768560208</v>
       </c>
       <c r="P42" t="n">
-        <v>782.6054414866707</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="Q42" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="R42" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="S42" t="n">
-        <v>678.5826554506689</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="T42" t="n">
-        <v>476.3960608094349</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="U42" t="n">
-        <v>476.3960608094349</v>
+        <v>638.1169902094293</v>
       </c>
       <c r="V42" t="n">
-        <v>476.3960608094349</v>
+        <v>638.1169902094293</v>
       </c>
       <c r="W42" t="n">
-        <v>476.3960608094349</v>
+        <v>422.536925949487</v>
       </c>
       <c r="X42" t="n">
-        <v>476.3960608094349</v>
+        <v>214.6854257439542</v>
       </c>
       <c r="Y42" t="n">
-        <v>476.3960608094349</v>
+        <v>214.6854257439542</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="C43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="D43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="E43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="F43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="G43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="H43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="I43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="L43" t="n">
-        <v>44.35412500771298</v>
+        <v>44.38806609710041</v>
       </c>
       <c r="M43" t="n">
-        <v>83.54216319993516</v>
+        <v>83.57610428932259</v>
       </c>
       <c r="N43" t="n">
-        <v>127.2330138553715</v>
+        <v>127.2669549447589</v>
       </c>
       <c r="O43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="P43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="Q43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="R43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="S43" t="n">
-        <v>17.04</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="T43" t="n">
-        <v>17.04</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="U43" t="n">
-        <v>17.04</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="V43" t="n">
-        <v>17.04</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="W43" t="n">
-        <v>17.04</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="X43" t="n">
-        <v>17.04</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="Y43" t="n">
-        <v>17.04</v>
+        <v>151.6062315796582</v>
       </c>
     </row>
     <row r="44">
@@ -8433,22 +8433,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K8" t="n">
-        <v>246.0898510449805</v>
+        <v>244.6749789590202</v>
       </c>
       <c r="L8" t="n">
         <v>235.7664149699872</v>
       </c>
       <c r="M8" t="n">
-        <v>256.3462332272727</v>
+        <v>255.9665244219036</v>
       </c>
       <c r="N8" t="n">
-        <v>254.3625585460859</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O8" t="n">
-        <v>230.0982114216867</v>
+        <v>255.7185026163176</v>
       </c>
       <c r="P8" t="n">
-        <v>257.2329957552695</v>
+        <v>256.8532869499004</v>
       </c>
       <c r="Q8" t="n">
         <v>212.3149906599047</v>
@@ -8515,22 +8515,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L9" t="n">
-        <v>164.5543797798742</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M9" t="n">
-        <v>168.1340339220183</v>
+        <v>167.7543251166491</v>
       </c>
       <c r="N9" t="n">
-        <v>156.2912070328283</v>
+        <v>155.926839997373</v>
       </c>
       <c r="O9" t="n">
         <v>142.5962444444444</v>
       </c>
       <c r="P9" t="n">
-        <v>133.9744074143302</v>
+        <v>159.5946986089611</v>
       </c>
       <c r="Q9" t="n">
-        <v>165.9817740860215</v>
+        <v>165.6020652806523</v>
       </c>
       <c r="R9" t="n">
         <v>45.52166981132082</v>
@@ -8594,13 +8594,13 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L10" t="n">
-        <v>160.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M10" t="n">
-        <v>164.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N10" t="n">
-        <v>153.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O10" t="n">
         <v>163.0416663658825</v>
@@ -8673,19 +8673,19 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L11" t="n">
-        <v>260.7159099194822</v>
+        <v>261.3867061646181</v>
       </c>
       <c r="M11" t="n">
-        <v>230.3462332272727</v>
+        <v>254.9313611413124</v>
       </c>
       <c r="N11" t="n">
-        <v>255.4130635965909</v>
+        <v>255.0333547912217</v>
       </c>
       <c r="O11" t="n">
-        <v>256.0982114216868</v>
+        <v>255.7185026163176</v>
       </c>
       <c r="P11" t="n">
-        <v>257.2329957552695</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q11" t="n">
         <v>212.3149906599047</v>
@@ -8749,19 +8749,19 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K12" t="n">
-        <v>163.841438974359</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L12" t="n">
-        <v>164.5543797798742</v>
+        <v>164.174670974505</v>
       </c>
       <c r="M12" t="n">
-        <v>168.1340339220183</v>
+        <v>167.7543251166491</v>
       </c>
       <c r="N12" t="n">
-        <v>156.2912070328283</v>
+        <v>156.9620032779641</v>
       </c>
       <c r="O12" t="n">
-        <v>142.5962444444444</v>
+        <v>167.1813723584841</v>
       </c>
       <c r="P12" t="n">
         <v>133.9744074143302</v>
@@ -8831,13 +8831,13 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L13" t="n">
-        <v>160.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M13" t="n">
-        <v>164.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N13" t="n">
-        <v>153.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O13" t="n">
         <v>163.0416663658825</v>
@@ -8907,22 +8907,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K14" t="n">
-        <v>246.0898510449805</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L14" t="n">
-        <v>261.7664149699872</v>
+        <v>261.3867061646181</v>
       </c>
       <c r="M14" t="n">
-        <v>255.2957281767677</v>
+        <v>255.9665244219036</v>
       </c>
       <c r="N14" t="n">
-        <v>229.4130635965909</v>
+        <v>253.9981915106306</v>
       </c>
       <c r="O14" t="n">
-        <v>230.0982114216867</v>
+        <v>255.7185026163176</v>
       </c>
       <c r="P14" t="n">
-        <v>257.2329957552695</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q14" t="n">
         <v>212.3149906599047</v>
@@ -8986,25 +8986,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K15" t="n">
-        <v>137.841438974359</v>
+        <v>162.4265668883987</v>
       </c>
       <c r="L15" t="n">
         <v>138.5543797798742</v>
       </c>
       <c r="M15" t="n">
-        <v>168.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N15" t="n">
-        <v>157.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O15" t="n">
-        <v>167.5457393939394</v>
+        <v>168.2165356390753</v>
       </c>
       <c r="P15" t="n">
-        <v>133.9744074143302</v>
+        <v>159.5946986089611</v>
       </c>
       <c r="Q15" t="n">
-        <v>165.9817740860215</v>
+        <v>165.6020652806523</v>
       </c>
       <c r="R15" t="n">
         <v>45.52166981132082</v>
@@ -9068,13 +9068,13 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L16" t="n">
-        <v>160.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M16" t="n">
-        <v>164.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N16" t="n">
-        <v>153.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O16" t="n">
         <v>163.0416663658825</v>
@@ -9144,22 +9144,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K17" t="n">
-        <v>248.0898510449805</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L17" t="n">
-        <v>235.7664149699872</v>
+        <v>262.2416917349371</v>
       </c>
       <c r="M17" t="n">
-        <v>257.2149200959596</v>
+        <v>257.9362584875889</v>
       </c>
       <c r="N17" t="n">
-        <v>257.4130635965909</v>
+        <v>257.0030888569071</v>
       </c>
       <c r="O17" t="n">
         <v>230.0982114216867</v>
       </c>
       <c r="P17" t="n">
-        <v>259.2329957552695</v>
+        <v>258.8230210155857</v>
       </c>
       <c r="Q17" t="n">
         <v>212.3149906599047</v>
@@ -9226,22 +9226,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L18" t="n">
-        <v>138.5543797798742</v>
+        <v>165.029656544824</v>
       </c>
       <c r="M18" t="n">
-        <v>169.0027207907052</v>
+        <v>169.7240591823345</v>
       </c>
       <c r="N18" t="n">
-        <v>159.3417120833333</v>
+        <v>158.9317373436494</v>
       </c>
       <c r="O18" t="n">
-        <v>170.5962444444444</v>
+        <v>170.1862697047606</v>
       </c>
       <c r="P18" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q18" t="n">
-        <v>167.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9308,10 +9308,10 @@
         <v>162.4747015415544</v>
       </c>
       <c r="M19" t="n">
-        <v>166.9257839476051</v>
+        <v>166.5158092079212</v>
       </c>
       <c r="N19" t="n">
-        <v>155.6855444652332</v>
+        <v>155.2755697255493</v>
       </c>
       <c r="O19" t="n">
         <v>163.0416663658825</v>
@@ -9393,7 +9393,7 @@
         <v>437.3469244119842</v>
       </c>
       <c r="O20" t="n">
-        <v>380.7436030804994</v>
+        <v>380.8001812627454</v>
       </c>
       <c r="P20" t="n">
         <v>321.7987081714826</v>
@@ -9460,25 +9460,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K21" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L21" t="n">
-        <v>138.5543797798742</v>
+        <v>243.2069195535496</v>
       </c>
       <c r="M21" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N21" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O21" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P21" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q21" t="n">
-        <v>186.7560391230408</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9618,7 +9618,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K23" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L23" t="n">
         <v>417.6612145504504</v>
@@ -9697,25 +9697,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K24" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L24" t="n">
-        <v>138.5543797798742</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M24" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N24" t="n">
-        <v>372.3417120833333</v>
+        <v>301.2485028631349</v>
       </c>
       <c r="O24" t="n">
-        <v>383.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P24" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q24" t="n">
-        <v>186.7560391230408</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9855,10 +9855,10 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K26" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L26" t="n">
-        <v>417.6612145504504</v>
+        <v>417.6612145504505</v>
       </c>
       <c r="M26" t="n">
         <v>449.5135334928325</v>
@@ -9937,22 +9937,22 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L27" t="n">
-        <v>138.5543797798742</v>
+        <v>173.111405903722</v>
       </c>
       <c r="M27" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N27" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O27" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P27" t="n">
-        <v>238.6132356387368</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q27" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R27" t="n">
         <v>45.52166981132082</v>
@@ -10095,7 +10095,7 @@
         <v>324.1454125711647</v>
       </c>
       <c r="L29" t="n">
-        <v>417.6046363682045</v>
+        <v>417.6612145504505</v>
       </c>
       <c r="M29" t="n">
         <v>449.5135334928325</v>
@@ -10174,22 +10174,22 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L30" t="n">
-        <v>138.5543797798742</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M30" t="n">
-        <v>233.1889872709904</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N30" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O30" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P30" t="n">
-        <v>318.4627686399372</v>
+        <v>247.3552705420797</v>
       </c>
       <c r="Q30" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10329,13 +10329,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K32" t="n">
-        <v>225.3066397049837</v>
+        <v>226.4727136557642</v>
       </c>
       <c r="L32" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M32" t="n">
-        <v>445.3462332272727</v>
+        <v>445.740230910301</v>
       </c>
       <c r="N32" t="n">
         <v>437.3469244119842</v>
@@ -10408,25 +10408,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K33" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L33" t="n">
-        <v>138.5543797798742</v>
+        <v>353.9483774629024</v>
       </c>
       <c r="M33" t="n">
-        <v>357.1340339220183</v>
+        <v>357.5280316050465</v>
       </c>
       <c r="N33" t="n">
-        <v>346.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O33" t="n">
-        <v>357.5962444444444</v>
+        <v>357.9902421274727</v>
       </c>
       <c r="P33" t="n">
-        <v>318.4627686399372</v>
+        <v>214.041819273966</v>
       </c>
       <c r="Q33" t="n">
-        <v>161.806544173546</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10566,13 +10566,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K35" t="n">
-        <v>324.1454125711647</v>
+        <v>226.4727136557642</v>
       </c>
       <c r="L35" t="n">
-        <v>318.8224416842694</v>
+        <v>417.6612145504504</v>
       </c>
       <c r="M35" t="n">
-        <v>445.3462332272727</v>
+        <v>445.740230910301</v>
       </c>
       <c r="N35" t="n">
         <v>437.3469244119842</v>
@@ -10648,13 +10648,13 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L36" t="n">
-        <v>353.5543797798742</v>
+        <v>353.9483774629024</v>
       </c>
       <c r="M36" t="n">
-        <v>357.1340339220183</v>
+        <v>357.5280316050465</v>
       </c>
       <c r="N36" t="n">
-        <v>241.5426841326382</v>
+        <v>242.3147604003903</v>
       </c>
       <c r="O36" t="n">
         <v>142.5962444444444</v>
@@ -10803,13 +10803,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K38" t="n">
-        <v>225.3066397049837</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L38" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M38" t="n">
-        <v>445.3462332272727</v>
+        <v>348.0675319949004</v>
       </c>
       <c r="N38" t="n">
         <v>437.3469244119842</v>
@@ -10888,16 +10888,16 @@
         <v>138.5543797798742</v>
       </c>
       <c r="M39" t="n">
-        <v>357.1340339220183</v>
+        <v>357.5280316050465</v>
       </c>
       <c r="N39" t="n">
-        <v>346.3417120833333</v>
+        <v>346.7357097663615</v>
       </c>
       <c r="O39" t="n">
-        <v>357.5962444444444</v>
+        <v>310.0975771498935</v>
       </c>
       <c r="P39" t="n">
-        <v>270.192025077634</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q39" t="n">
         <v>210.0772877358491</v>
@@ -11040,13 +11040,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K41" t="n">
-        <v>324.1454125711647</v>
+        <v>220.6430966734834</v>
       </c>
       <c r="L41" t="n">
-        <v>312.9032497650775</v>
+        <v>417.6612145504504</v>
       </c>
       <c r="M41" t="n">
-        <v>443.3462332272727</v>
+        <v>443.7704968446156</v>
       </c>
       <c r="N41" t="n">
         <v>437.3469244119842</v>
@@ -11119,25 +11119,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K42" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L42" t="n">
-        <v>351.5543797798742</v>
+        <v>245.6675451803358</v>
       </c>
       <c r="M42" t="n">
         <v>142.1340339220183</v>
       </c>
       <c r="N42" t="n">
-        <v>294.1517766018381</v>
+        <v>344.7659757006762</v>
       </c>
       <c r="O42" t="n">
-        <v>355.5962444444444</v>
+        <v>356.0205080617874</v>
       </c>
       <c r="P42" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q42" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -22981,13 +22981,13 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C8" t="n">
-        <v>354.3213811256201</v>
+        <v>339.6526005763767</v>
       </c>
       <c r="D8" t="n">
-        <v>328.683041620683</v>
+        <v>342.1073883509969</v>
       </c>
       <c r="E8" t="n">
-        <v>355.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F8" t="n">
         <v>406.8760457417114</v>
@@ -22999,10 +22999,10 @@
         <v>339.4748021157671</v>
       </c>
       <c r="I8" t="n">
-        <v>210.4758895704059</v>
+        <v>184.8555983757751</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -23023,10 +23023,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>123.8691179411497</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S8" t="n">
         <v>209.0200695862453</v>
@@ -23047,7 +23047,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y8" t="n">
-        <v>386.2379386560536</v>
+        <v>360.6176474614227</v>
       </c>
     </row>
     <row r="9">
@@ -23069,16 +23069,16 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F9" t="n">
-        <v>122.9150037196417</v>
+        <v>123.2494512354109</v>
       </c>
       <c r="G9" t="n">
-        <v>111.3435171632106</v>
+        <v>111.7232259685798</v>
       </c>
       <c r="H9" t="n">
-        <v>86.23544423649646</v>
+        <v>86.61515304186563</v>
       </c>
       <c r="I9" t="n">
-        <v>63.39663285141508</v>
+        <v>63.77634165678425</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -23151,16 +23151,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G10" t="n">
-        <v>145.4472954899085</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H10" t="n">
-        <v>136.2271725074396</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I10" t="n">
-        <v>129.4504749272583</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J10" t="n">
-        <v>67.35918011667277</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K10" t="n">
         <v>22.26949182588285</v>
@@ -23178,19 +23178,19 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>86.16204325169439</v>
+        <v>60.54175205706355</v>
       </c>
       <c r="R10" t="n">
-        <v>177.2933913771695</v>
+        <v>151.6731001825387</v>
       </c>
       <c r="S10" t="n">
-        <v>224.0165980369723</v>
+        <v>198.3963068423414</v>
       </c>
       <c r="T10" t="n">
-        <v>227.9455894282815</v>
+        <v>208.1006776791572</v>
       </c>
       <c r="U10" t="n">
         <v>286.3190293564909</v>
@@ -23263,16 +23263,16 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R11" t="n">
-        <v>126.9683179411497</v>
+        <v>127.3027654569188</v>
       </c>
       <c r="S11" t="n">
-        <v>183.0200695862453</v>
+        <v>183.3997783916145</v>
       </c>
       <c r="T11" t="n">
-        <v>197.0958495641314</v>
+        <v>197.4755583695005</v>
       </c>
       <c r="U11" t="n">
-        <v>225.3456529078365</v>
+        <v>225.7253617132057</v>
       </c>
       <c r="V11" t="n">
         <v>327.7522584701349</v>
@@ -23306,16 +23306,16 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F12" t="n">
-        <v>145.0692123933839</v>
+        <v>122.502859909153</v>
       </c>
       <c r="G12" t="n">
-        <v>137.3435171632106</v>
+        <v>111.7232259685798</v>
       </c>
       <c r="H12" t="n">
-        <v>112.2354442364965</v>
+        <v>86.61515304186563</v>
       </c>
       <c r="I12" t="n">
-        <v>89.39663285141508</v>
+        <v>63.77634165678425</v>
       </c>
       <c r="J12" t="n">
         <v>0.7465913262578567</v>
@@ -23342,16 +23342,16 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>74.15783415264313</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S12" t="n">
-        <v>145.6831711038378</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T12" t="n">
-        <v>174.1647286948216</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U12" t="n">
-        <v>203.0405820809748</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V12" t="n">
         <v>232.8005871494253</v>
@@ -23391,16 +23391,16 @@
         <v>167.9909793584588</v>
       </c>
       <c r="H13" t="n">
-        <v>138.6744211998787</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I13" t="n">
-        <v>129.4504749272583</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J13" t="n">
-        <v>67.35918011667277</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -23418,16 +23418,16 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>86.16204325169439</v>
+        <v>60.54175205706355</v>
       </c>
       <c r="R13" t="n">
-        <v>177.2933913771695</v>
+        <v>151.6731001825387</v>
       </c>
       <c r="S13" t="n">
-        <v>224.0165980369723</v>
+        <v>198.3963068423414</v>
       </c>
       <c r="T13" t="n">
-        <v>227.9455894282815</v>
+        <v>208.1006776791572</v>
       </c>
       <c r="U13" t="n">
         <v>286.3190293564909</v>
@@ -23500,16 +23500,16 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R14" t="n">
-        <v>126.9683179411497</v>
+        <v>127.3027654569188</v>
       </c>
       <c r="S14" t="n">
-        <v>183.0200695862453</v>
+        <v>183.3997783916145</v>
       </c>
       <c r="T14" t="n">
-        <v>197.0958495641314</v>
+        <v>197.4755583695005</v>
       </c>
       <c r="U14" t="n">
-        <v>225.3456529078365</v>
+        <v>225.7253617132057</v>
       </c>
       <c r="V14" t="n">
         <v>327.7522584701349</v>
@@ -23555,7 +23555,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -23579,16 +23579,16 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>74.15783415264313</v>
+        <v>74.5375429580123</v>
       </c>
       <c r="S15" t="n">
-        <v>145.6831711038378</v>
+        <v>146.062879909207</v>
       </c>
       <c r="T15" t="n">
-        <v>174.1647286948216</v>
+        <v>174.5444375001908</v>
       </c>
       <c r="U15" t="n">
-        <v>203.7871734072327</v>
+        <v>203.375029596744</v>
       </c>
       <c r="V15" t="n">
         <v>232.8005871494253</v>
@@ -23625,19 +23625,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G16" t="n">
-        <v>167.7167873157914</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H16" t="n">
-        <v>136.2271725074396</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I16" t="n">
-        <v>129.4504749272583</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J16" t="n">
-        <v>67.35918011667277</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -23655,16 +23655,16 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q16" t="n">
-        <v>86.16204325169439</v>
+        <v>60.54175205706355</v>
       </c>
       <c r="R16" t="n">
-        <v>177.2933913771695</v>
+        <v>151.6731001825387</v>
       </c>
       <c r="S16" t="n">
-        <v>224.0165980369723</v>
+        <v>198.3963068423414</v>
       </c>
       <c r="T16" t="n">
-        <v>227.9455894282815</v>
+        <v>205.3792369440507</v>
       </c>
       <c r="U16" t="n">
         <v>286.3190293564909</v>
@@ -23737,16 +23737,16 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>121.8691179411497</v>
+        <v>122.2790926808335</v>
       </c>
       <c r="S17" t="n">
-        <v>181.0200695862453</v>
+        <v>181.4300443259292</v>
       </c>
       <c r="T17" t="n">
-        <v>195.0958495641314</v>
+        <v>195.5058243038152</v>
       </c>
       <c r="U17" t="n">
-        <v>236.6739521223813</v>
+        <v>237.0350578730948</v>
       </c>
       <c r="V17" t="n">
         <v>327.7522584701349</v>
@@ -23777,19 +23777,19 @@
         <v>147.4450655646388</v>
       </c>
       <c r="E18" t="n">
-        <v>129.6450804554009</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F18" t="n">
-        <v>117.0692123933839</v>
+        <v>117.4791871330677</v>
       </c>
       <c r="G18" t="n">
-        <v>137.3435171632106</v>
+        <v>109.7534919028945</v>
       </c>
       <c r="H18" t="n">
         <v>112.2354442364965</v>
       </c>
       <c r="I18" t="n">
-        <v>89.39663285141508</v>
+        <v>61.80660759109894</v>
       </c>
       <c r="J18" t="n">
         <v>0.7465913262578567</v>
@@ -23816,10 +23816,10 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>72.15783415264313</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S18" t="n">
-        <v>147.0207711038378</v>
+        <v>147.3818768545514</v>
       </c>
       <c r="T18" t="n">
         <v>200.1647286948216</v>
@@ -23847,7 +23847,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>157.8095125557512</v>
+        <v>152.2419549216212</v>
       </c>
       <c r="C19" t="n">
         <v>167.2468210986278</v>
@@ -23865,7 +23865,7 @@
         <v>167.9909793584588</v>
       </c>
       <c r="H19" t="n">
-        <v>162.2271725074396</v>
+        <v>139.7784131469302</v>
       </c>
       <c r="I19" t="n">
         <v>155.4504749272583</v>
@@ -23907,16 +23907,16 @@
         <v>286.3190293564909</v>
       </c>
       <c r="V19" t="n">
-        <v>252.137643323828</v>
+        <v>224.5476180635119</v>
       </c>
       <c r="W19" t="n">
-        <v>258.522998336591</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X19" t="n">
-        <v>197.7096553890372</v>
+        <v>225.7096553890372</v>
       </c>
       <c r="Y19" t="n">
-        <v>190.5846533520948</v>
+        <v>190.9946280917787</v>
       </c>
     </row>
     <row r="20">
@@ -23932,25 +23932,25 @@
         <v>365.2728917710076</v>
       </c>
       <c r="D20" t="n">
-        <v>354.683041620683</v>
+        <v>154.3469453318533</v>
       </c>
       <c r="E20" t="n">
-        <v>140.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F20" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G20" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H20" t="n">
         <v>339.4748021157671</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J20" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -23977,10 +23977,10 @@
         <v>149.8691179411497</v>
       </c>
       <c r="S20" t="n">
-        <v>189.3190087207827</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U20" t="n">
         <v>251.3456529078365</v>
@@ -23995,7 +23995,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y20" t="n">
-        <v>145.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="21">
@@ -24005,13 +24005,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>115.8327620500724</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>157.6450804554009</v>
@@ -24023,13 +24023,13 @@
         <v>137.3435171632106</v>
       </c>
       <c r="H21" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>89.39663285141508</v>
+        <v>54.05972718803677</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -24053,28 +24053,28 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>171.6831711038378</v>
       </c>
       <c r="T21" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V21" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W21" t="n">
-        <v>10.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="22">
@@ -24147,10 +24147,10 @@
         <v>252.137643323828</v>
       </c>
       <c r="W22" t="n">
-        <v>286.522998336591</v>
+        <v>153.336030751223</v>
       </c>
       <c r="X22" t="n">
-        <v>92.52268780366913</v>
+        <v>225.7096553890372</v>
       </c>
       <c r="Y22" t="n">
         <v>218.5846533520948</v>
@@ -24172,22 +24172,22 @@
         <v>354.683041620683</v>
       </c>
       <c r="E23" t="n">
-        <v>140.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F23" t="n">
-        <v>165.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G23" t="n">
         <v>415.302737515135</v>
       </c>
       <c r="H23" t="n">
-        <v>139.1512914703796</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I23" t="n">
         <v>210.4758895704059</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -24208,22 +24208,22 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>251.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V23" t="n">
-        <v>327.7522584701349</v>
+        <v>225.414031377446</v>
       </c>
       <c r="W23" t="n">
         <v>349.240968717413</v>
@@ -24232,7 +24232,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y23" t="n">
-        <v>145.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="24">
@@ -24245,16 +24245,16 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>50.77514371154891</v>
       </c>
       <c r="D24" t="n">
         <v>147.4450655646388</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
         <v>137.3435171632106</v>
@@ -24263,10 +24263,10 @@
         <v>112.2354442364965</v>
       </c>
       <c r="I24" t="n">
-        <v>68.66740492112176</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -24290,13 +24290,13 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T24" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
         <v>225.9413820809748</v>
@@ -24305,13 +24305,13 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W24" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X24" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y24" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -24369,7 +24369,7 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R25" t="n">
-        <v>177.2933913771695</v>
+        <v>44.10642379180146</v>
       </c>
       <c r="S25" t="n">
         <v>224.0165980369723</v>
@@ -24381,7 +24381,7 @@
         <v>286.3190293564909</v>
       </c>
       <c r="V25" t="n">
-        <v>118.95067573846</v>
+        <v>252.137643323828</v>
       </c>
       <c r="W25" t="n">
         <v>286.522998336591</v>
@@ -24400,7 +24400,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>382.7338416634806</v>
+        <v>141.7195527858215</v>
       </c>
       <c r="C26" t="n">
         <v>365.2728917710076</v>
@@ -24412,19 +24412,19 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F26" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G26" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H26" t="n">
-        <v>98.47480211576715</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I26" t="n">
-        <v>160.0214968661681</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -24448,7 +24448,7 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S26" t="n">
         <v>209.0200695862453</v>
@@ -24460,16 +24460,16 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V26" t="n">
-        <v>327.7522584701349</v>
+        <v>115.4668728266929</v>
       </c>
       <c r="W26" t="n">
-        <v>108.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X26" t="n">
         <v>369.731100678469</v>
       </c>
       <c r="Y26" t="n">
-        <v>386.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="27">
@@ -24485,25 +24485,25 @@
         <v>172.7084989883157</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>56.19487622506016</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>31.60576090318308</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>89.39663285141508</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -24530,7 +24530,7 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T27" t="n">
         <v>200.1647286948216</v>
@@ -24548,7 +24548,7 @@
         <v>205.7729852034775</v>
       </c>
       <c r="Y27" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -24579,7 +24579,7 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I28" t="n">
-        <v>155.4504749272583</v>
+        <v>22.26350734189026</v>
       </c>
       <c r="J28" t="n">
         <v>93.35918011667277</v>
@@ -24621,7 +24621,7 @@
         <v>252.137643323828</v>
       </c>
       <c r="W28" t="n">
-        <v>153.336030751223</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X28" t="n">
         <v>225.7096553890372</v>
@@ -24637,19 +24637,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>382.7338416634806</v>
+        <v>170.4484560200386</v>
       </c>
       <c r="C29" t="n">
         <v>365.2728917710076</v>
       </c>
       <c r="D29" t="n">
-        <v>354.683041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E29" t="n">
-        <v>140.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F29" t="n">
-        <v>165.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G29" t="n">
         <v>415.302737515135</v>
@@ -24691,7 +24691,7 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U29" t="n">
         <v>251.3456529078365</v>
@@ -24706,7 +24706,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y29" t="n">
-        <v>156.060988220185</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="30">
@@ -24716,28 +24716,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D30" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>85.11742366028636</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0.7465913262578567</v>
@@ -24767,7 +24767,7 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S30" t="n">
-        <v>171.6831711038378</v>
+        <v>113.2212462480057</v>
       </c>
       <c r="T30" t="n">
         <v>200.1647286948216</v>
@@ -24776,16 +24776,16 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V30" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>10.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X30" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="31">
@@ -24813,7 +24813,7 @@
         <v>167.9909793584588</v>
       </c>
       <c r="H31" t="n">
-        <v>29.04020492207158</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I31" t="n">
         <v>155.4504749272583</v>
@@ -24864,7 +24864,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y31" t="n">
-        <v>218.5846533520948</v>
+        <v>85.39768576672677</v>
       </c>
     </row>
     <row r="32">
@@ -24889,13 +24889,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G32" t="n">
-        <v>200.302737515135</v>
+        <v>199.9087398321068</v>
       </c>
       <c r="H32" t="n">
-        <v>124.4748021157671</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I32" t="n">
-        <v>180.9637067261005</v>
+        <v>14.38292831441186</v>
       </c>
       <c r="J32" t="n">
         <v>11.94928935461252</v>
@@ -24919,19 +24919,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S32" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>223.0958495641314</v>
+        <v>7.701851881103124</v>
       </c>
       <c r="U32" t="n">
-        <v>36.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V32" t="n">
         <v>327.7522584701349</v>
@@ -24953,22 +24953,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C33" t="n">
         <v>172.7084989883157</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E33" t="n">
         <v>157.6450804554009</v>
       </c>
       <c r="F33" t="n">
-        <v>145.0692123933839</v>
+        <v>2.085884901901551</v>
       </c>
       <c r="G33" t="n">
-        <v>37.72275158119429</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H33" t="n">
         <v>112.2354442364965</v>
@@ -25001,28 +25001,28 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U33" t="n">
-        <v>225.9413820809748</v>
+        <v>10.54738439794659</v>
       </c>
       <c r="V33" t="n">
-        <v>17.80058714942527</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W33" t="n">
         <v>251.6949831609196</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y33" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -25074,13 +25074,13 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>177.2933913771695</v>
+        <v>132.9899077786024</v>
       </c>
       <c r="S34" t="n">
         <v>224.0165980369723</v>
@@ -25098,7 +25098,7 @@
         <v>286.522998336591</v>
       </c>
       <c r="X34" t="n">
-        <v>92.52268780366916</v>
+        <v>225.7096553890372</v>
       </c>
       <c r="Y34" t="n">
         <v>218.5846533520948</v>
@@ -25114,16 +25114,16 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C35" t="n">
-        <v>329.7807785129474</v>
+        <v>185.5445578263411</v>
       </c>
       <c r="D35" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E35" t="n">
-        <v>166.9303700722618</v>
+        <v>166.5363723892335</v>
       </c>
       <c r="F35" t="n">
-        <v>406.8760457417114</v>
+        <v>191.4820480586832</v>
       </c>
       <c r="G35" t="n">
         <v>415.302737515135</v>
@@ -25159,10 +25159,10 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T35" t="n">
         <v>223.0958495641314</v>
@@ -25180,7 +25180,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y35" t="n">
-        <v>171.2379386560536</v>
+        <v>170.8439409730254</v>
       </c>
     </row>
     <row r="36">
@@ -25190,25 +25190,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>172.7084989883157</v>
+        <v>165.8932932324504</v>
       </c>
       <c r="D36" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>137.3435171632106</v>
       </c>
       <c r="H36" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>89.39663285141508</v>
@@ -25247,16 +25247,16 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U36" t="n">
-        <v>10.94138208097482</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V36" t="n">
-        <v>17.80058714942527</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W36" t="n">
-        <v>36.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X36" t="n">
-        <v>116.5588193561207</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y36" t="n">
         <v>205.6826957773044</v>
@@ -25314,10 +25314,10 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q37" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>177.2933913771695</v>
+        <v>130.2684670434958</v>
       </c>
       <c r="S37" t="n">
         <v>224.0165980369723</v>
@@ -25329,7 +25329,7 @@
         <v>286.3190293564909</v>
       </c>
       <c r="V37" t="n">
-        <v>118.95067573846</v>
+        <v>252.137643323828</v>
       </c>
       <c r="W37" t="n">
         <v>286.522998336591</v>
@@ -25348,25 +25348,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>382.7338416634806</v>
+        <v>167.3398439804523</v>
       </c>
       <c r="C38" t="n">
         <v>365.2728917710076</v>
       </c>
       <c r="D38" t="n">
-        <v>139.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E38" t="n">
-        <v>166.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F38" t="n">
         <v>406.8760457417114</v>
       </c>
       <c r="G38" t="n">
-        <v>200.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H38" t="n">
-        <v>339.4748021157671</v>
+        <v>124.0808044327389</v>
       </c>
       <c r="I38" t="n">
         <v>210.4758895704059</v>
@@ -25399,7 +25399,7 @@
         <v>149.8691179411497</v>
       </c>
       <c r="S38" t="n">
-        <v>19.64806958624538</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T38" t="n">
         <v>223.0958495641314</v>
@@ -25411,13 +25411,13 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W38" t="n">
-        <v>349.240968717413</v>
+        <v>159.5219355582018</v>
       </c>
       <c r="X38" t="n">
         <v>369.731100678469</v>
       </c>
       <c r="Y38" t="n">
-        <v>386.2379386560536</v>
+        <v>170.8439409730254</v>
       </c>
     </row>
     <row r="39">
@@ -25427,13 +25427,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
         <v>172.7084989883157</v>
       </c>
       <c r="D39" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
         <v>157.6450804554009</v>
@@ -25442,16 +25442,16 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H39" t="n">
-        <v>112.2354442364965</v>
+        <v>6.617984946814303</v>
       </c>
       <c r="I39" t="n">
         <v>89.39663285141508</v>
       </c>
       <c r="J39" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -25478,25 +25478,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S39" t="n">
-        <v>110.3373840443529</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T39" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>10.94138208097482</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V39" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W39" t="n">
-        <v>36.69498316091961</v>
+        <v>36.30098547789137</v>
       </c>
       <c r="X39" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="40">
@@ -25527,7 +25527,7 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I40" t="n">
-        <v>22.26350734189026</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J40" t="n">
         <v>93.35918011667277</v>
@@ -25554,7 +25554,7 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R40" t="n">
-        <v>177.2933913771695</v>
+        <v>44.10642379180146</v>
       </c>
       <c r="S40" t="n">
         <v>224.0165980369723</v>
@@ -25597,10 +25597,10 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F41" t="n">
-        <v>222.7523041129076</v>
+        <v>193.4517821243685</v>
       </c>
       <c r="G41" t="n">
-        <v>202.302737515135</v>
+        <v>201.8784738977921</v>
       </c>
       <c r="H41" t="n">
         <v>339.4748021157671</v>
@@ -25630,13 +25630,13 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R41" t="n">
         <v>149.8691179411497</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T41" t="n">
         <v>223.0958495641314</v>
@@ -25654,7 +25654,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y41" t="n">
-        <v>386.2379386560536</v>
+        <v>195.305473214961</v>
       </c>
     </row>
     <row r="42">
@@ -25673,22 +25673,22 @@
         <v>147.4450655646388</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>107.0789230407638</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H42" t="n">
         <v>112.2354442364965</v>
       </c>
       <c r="I42" t="n">
-        <v>75.43853398832785</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -25715,22 +25715,22 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U42" t="n">
-        <v>225.9413820809748</v>
+        <v>12.5171184636319</v>
       </c>
       <c r="V42" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W42" t="n">
-        <v>251.6949831609196</v>
+        <v>38.27071954357669</v>
       </c>
       <c r="X42" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
         <v>205.6826957773044</v>
@@ -25743,7 +25743,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>179.8319801819373</v>
+        <v>46.64501259656927</v>
       </c>
       <c r="C43" t="n">
         <v>167.2468210986278</v>
@@ -25794,7 +25794,7 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S43" t="n">
-        <v>90.82963045160423</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T43" t="n">
         <v>227.9455894282815</v>
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>350350.0795405007</v>
+        <v>350035.0587549793</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>350350.0795405007</v>
+        <v>350035.0587549793</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>350350.0795405007</v>
+        <v>350035.0587549793</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>351994.6487060301</v>
+        <v>351669.2246312142</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>506779.7343245363</v>
+        <v>506790.0512205642</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>506779.7343245363</v>
+        <v>506790.0512205642</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>506779.7343245363</v>
+        <v>506790.0512205641</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>506779.7343245365</v>
+        <v>506790.0512205642</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>488007.1404845364</v>
+        <v>488291.61581059</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>488007.1404845364</v>
+        <v>488291.61581059</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>488007.1404845365</v>
+        <v>488291.6158105898</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>486563.0948045364</v>
+        <v>486869.4228264389</v>
       </c>
     </row>
     <row r="16">
@@ -26267,43 +26267,43 @@
         <v>48378.33248915088</v>
       </c>
       <c r="D2" t="n">
-        <v>51690.99534204105</v>
+        <v>51644.51686548872</v>
       </c>
       <c r="E2" t="n">
-        <v>51690.99534204105</v>
+        <v>51644.51686548874</v>
       </c>
       <c r="F2" t="n">
-        <v>51690.99534204105</v>
+        <v>51644.51686548873</v>
       </c>
       <c r="G2" t="n">
-        <v>51933.63669433229</v>
+        <v>51885.62330624469</v>
       </c>
       <c r="H2" t="n">
-        <v>74770.78047411186</v>
+        <v>74772.30263909957</v>
       </c>
       <c r="I2" t="n">
-        <v>74770.78047411186</v>
+        <v>74772.30263909959</v>
       </c>
       <c r="J2" t="n">
-        <v>74770.78047411186</v>
+        <v>74772.30263909961</v>
       </c>
       <c r="K2" t="n">
-        <v>74770.78047411187</v>
+        <v>74772.30263909958</v>
       </c>
       <c r="L2" t="n">
-        <v>72001.05351411186</v>
+        <v>72043.02528352961</v>
       </c>
       <c r="M2" t="n">
-        <v>72001.05351411185</v>
+        <v>72043.02528352957</v>
       </c>
       <c r="N2" t="n">
-        <v>72001.05351411187</v>
+        <v>72043.02528352961</v>
       </c>
       <c r="O2" t="n">
-        <v>71787.99759411186</v>
+        <v>71833.1935317696</v>
       </c>
       <c r="P2" t="n">
-        <v>48378.33248915087</v>
+        <v>48378.33248915088</v>
       </c>
     </row>
     <row r="3">
@@ -26319,7 +26319,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>8076.38</v>
+        <v>7958.431053788175</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -26328,10 +26328,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>548.1700000000001</v>
+        <v>539.8745613933579</v>
       </c>
       <c r="H3" t="n">
-        <v>57469.317</v>
+        <v>57583.78714233168</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -26371,40 +26371,40 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>22.532822180663</v>
+        <v>22.21667432804714</v>
       </c>
       <c r="E4" t="n">
-        <v>22.532822180663</v>
+        <v>22.21667432804715</v>
       </c>
       <c r="F4" t="n">
-        <v>22.532822180663</v>
+        <v>22.21667432804714</v>
       </c>
       <c r="G4" t="n">
-        <v>24.1832752112465</v>
+        <v>23.85668684891895</v>
       </c>
       <c r="H4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="I4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="J4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="K4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="L4" t="n">
-        <v>160.6823863208583</v>
+        <v>160.9678794298453</v>
       </c>
       <c r="M4" t="n">
-        <v>160.6823863208583</v>
+        <v>160.9678794298453</v>
       </c>
       <c r="N4" t="n">
-        <v>160.6823863208583</v>
+        <v>160.9678794298453</v>
       </c>
       <c r="O4" t="n">
-        <v>159.2331741996462</v>
+        <v>159.5405981880675</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -26423,40 +26423,40 @@
         <v>33627.6</v>
       </c>
       <c r="D5" t="n">
-        <v>35208.4</v>
+        <v>35185.31370463355</v>
       </c>
       <c r="E5" t="n">
-        <v>1580.8</v>
+        <v>1557.713704633554</v>
       </c>
       <c r="F5" t="n">
-        <v>1580.8</v>
+        <v>1557.713704633554</v>
       </c>
       <c r="G5" t="n">
-        <v>1702.4</v>
+        <v>1677.473535827221</v>
       </c>
       <c r="H5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="I5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="J5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="K5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="L5" t="n">
-        <v>13072</v>
+        <v>13095.95505912812</v>
       </c>
       <c r="M5" t="n">
-        <v>13072</v>
+        <v>13095.95505912812</v>
       </c>
       <c r="N5" t="n">
-        <v>13072</v>
+        <v>13095.95505912812</v>
       </c>
       <c r="O5" t="n">
-        <v>12950.4</v>
+        <v>12976.19522793445</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -26475,43 +26475,43 @@
         <v>14750.73248915088</v>
       </c>
       <c r="D6" t="n">
-        <v>8383.682519860384</v>
+        <v>8478.555432738947</v>
       </c>
       <c r="E6" t="n">
-        <v>50087.66251986038</v>
+        <v>50064.58648652714</v>
       </c>
       <c r="F6" t="n">
-        <v>50087.66251986038</v>
+        <v>50064.58648652713</v>
       </c>
       <c r="G6" t="n">
-        <v>49658.88341912105</v>
+        <v>49644.41852217519</v>
       </c>
       <c r="H6" t="n">
-        <v>2469.141330215243</v>
+        <v>2355.314235302245</v>
       </c>
       <c r="I6" t="n">
-        <v>59938.45833021525</v>
+        <v>59939.10137763395</v>
       </c>
       <c r="J6" t="n">
-        <v>59938.45833021525</v>
+        <v>59939.10137763397</v>
       </c>
       <c r="K6" t="n">
-        <v>59938.45833021526</v>
+        <v>59939.10137763394</v>
       </c>
       <c r="L6" t="n">
-        <v>58768.371127791</v>
+        <v>58786.10234497164</v>
       </c>
       <c r="M6" t="n">
-        <v>58768.37112779099</v>
+        <v>58786.1023449716</v>
       </c>
       <c r="N6" t="n">
-        <v>58768.37112779102</v>
+        <v>58786.10234497164</v>
       </c>
       <c r="O6" t="n">
-        <v>58678.36441991221</v>
+        <v>58697.4577056471</v>
       </c>
       <c r="P6" t="n">
-        <v>48378.33248915087</v>
+        <v>48378.33248915088</v>
       </c>
     </row>
   </sheetData>
@@ -26733,40 +26733,40 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="E4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="G4" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="L4" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="M4" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N4" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="O4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26892,13 +26892,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -26922,19 +26922,19 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26950,43 +26950,43 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1.969734065685309</v>
       </c>
       <c r="H4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27191,7 +27191,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -27200,10 +27200,10 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>1.969734065685309</v>
       </c>
       <c r="P4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
     </row>
   </sheetData>
@@ -35088,22 +35088,22 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>26</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N8" t="n">
-        <v>24.94949494949495</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P8" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -35170,22 +35170,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N9" t="n">
-        <v>24.94949494949495</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q9" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -35249,13 +35249,13 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M10" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N10" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O10" t="n">
         <v>24.58512791403967</v>
@@ -35328,19 +35328,19 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>24.94949494949496</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="N11" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O11" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -35404,19 +35404,19 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M12" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N12" t="n">
-        <v>24.94949494949495</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -35486,16 +35486,16 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O13" t="n">
-        <v>24.58512791403967</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -35562,22 +35562,22 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M14" t="n">
-        <v>24.94949494949495</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -35641,25 +35641,25 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>24.94949494949495</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q15" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35723,13 +35723,13 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O16" t="n">
         <v>24.58512791403967</v>
@@ -35799,22 +35799,22 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>26.47527676494984</v>
       </c>
       <c r="M17" t="n">
-        <v>26.86868686868687</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -35881,22 +35881,22 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>26.47527676494984</v>
       </c>
       <c r="M18" t="n">
-        <v>26.86868686868687</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N18" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O18" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -35963,10 +35963,10 @@
         <v>27.59002526031614</v>
       </c>
       <c r="M19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O19" t="n">
         <v>24.58512791403967</v>
@@ -36048,7 +36048,7 @@
         <v>207.9338608153932</v>
       </c>
       <c r="O20" t="n">
-        <v>150.6453916588127</v>
+        <v>150.7019698410586</v>
       </c>
       <c r="P20" t="n">
         <v>90.5657124162131</v>
@@ -36115,25 +36115,25 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>104.6525397736754</v>
       </c>
       <c r="M21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P21" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>46.77426503701921</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36273,7 +36273,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L23" t="n">
         <v>181.8947995804632</v>
@@ -36352,25 +36352,25 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M24" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N24" t="n">
-        <v>241</v>
+        <v>169.9067907798016</v>
       </c>
       <c r="O24" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q24" t="n">
-        <v>46.77426503701921</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36510,7 +36510,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L26" t="n">
         <v>181.8947995804632</v>
@@ -36592,22 +36592,22 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>34.55702612384782</v>
       </c>
       <c r="M27" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N27" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O27" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P27" t="n">
-        <v>104.6388282244066</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -36750,7 +36750,7 @@
         <v>104.0555615261842</v>
       </c>
       <c r="L29" t="n">
-        <v>181.8382213982173</v>
+        <v>181.8947995804632</v>
       </c>
       <c r="M29" t="n">
         <v>219.1673002655598</v>
@@ -36829,22 +36829,22 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M30" t="n">
-        <v>91.05495334897203</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O30" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P30" t="n">
-        <v>184.4883612256069</v>
+        <v>113.3808631277494</v>
       </c>
       <c r="Q30" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -36984,13 +36984,13 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>5.216788660003122</v>
+        <v>6.382862610783645</v>
       </c>
       <c r="L32" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M32" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N32" t="n">
         <v>207.9338608153932</v>
@@ -37063,25 +37063,25 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="M33" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N33" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="P33" t="n">
-        <v>184.4883612256069</v>
+        <v>80.06741185963574</v>
       </c>
       <c r="Q33" t="n">
-        <v>21.82477008752445</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37221,13 +37221,13 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>104.0555615261842</v>
+        <v>6.382862610783645</v>
       </c>
       <c r="L35" t="n">
-        <v>83.05602671428214</v>
+        <v>181.8947995804632</v>
       </c>
       <c r="M35" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N35" t="n">
         <v>207.9338608153932</v>
@@ -37303,13 +37303,13 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L36" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="M36" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N36" t="n">
-        <v>110.2009720493049</v>
+        <v>110.973048317057</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -37458,13 +37458,13 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>5.216788660003122</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L38" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M38" t="n">
-        <v>215</v>
+        <v>117.7212987676277</v>
       </c>
       <c r="N38" t="n">
         <v>207.9338608153932</v>
@@ -37543,16 +37543,16 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N39" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="O39" t="n">
-        <v>215</v>
+        <v>167.5013327054491</v>
       </c>
       <c r="P39" t="n">
-        <v>136.2176176633037</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q39" t="n">
         <v>70.09551364982758</v>
@@ -37695,13 +37695,13 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>104.0555615261842</v>
+        <v>0.5532456285028686</v>
       </c>
       <c r="L41" t="n">
-        <v>77.13683479509021</v>
+        <v>181.8947995804632</v>
       </c>
       <c r="M41" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="N41" t="n">
         <v>207.9338608153932</v>
@@ -37774,25 +37774,25 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L42" t="n">
-        <v>213</v>
+        <v>107.1131654004616</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>162.8100645185048</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="O42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="P42" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q42" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
